--- a/examples/excel/charts/charts-extended.xlsx
+++ b/examples/excel/charts/charts-extended.xlsx
@@ -1,17 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet name="1-Waterfall &amp; Funnel" sheetId="2" r:id="R853d1717e2bd4bd3"/>
-    <x:sheet name="2-Treemap &amp; Sunburst" sheetId="3" r:id="R2ab12bc998b349e8"/>
-    <x:sheet name="3-Histogram &amp; BoxWhisker" sheetId="4" r:id="Rb74cb9a3ad0a46f3"/>
-    <x:sheet name="4-Pareto" sheetId="5" r:id="Rde364c0f12174177"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-Waterfall &amp; Funnel" sheetId="2" r:id="R38a288d9d7824b0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-Treemap &amp; Sunburst" sheetId="3" r:id="R63f0dfea0f6b4c36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-Histogram &amp; BoxWhisker" sheetId="4" r:id="R01a3eea11b524030"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-Pareto" sheetId="5" r:id="R26db7af80c6b4d15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5-Chart Meta" sheetId="6" r:id="R7c09be016ba74e9a"/>
   </x:sheets>
 </x:workbook>
 </file>
 
 <file path=xl/drawings/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <c:chart>
     <c:title>
       <c:tx>
@@ -273,7 +274,7 @@
 </file>
 
 <file path=xl/drawings/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <c:chart>
     <c:title>
       <c:tx>
@@ -544,8 +545,742 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/drawings/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="44546A"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>anchor + preset=corporate</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Revenue</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="2E75B6"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>Q1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Q2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>Q3</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>Q4</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>120</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>145</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>132</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>160</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="150"/>
+        <c:axId val="1"/>
+        <c:axId val="2"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+            <a:solidFill>
+              <a:srgbClr val="8B949E"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1000">
+                <a:solidFill>
+                  <a:srgbClr val="44546A"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="5080">
+              <a:solidFill>
+                <a:srgbClr val="D6DCE4"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+            <a:solidFill>
+              <a:srgbClr val="8B949E"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1000">
+                <a:solidFill>
+                  <a:srgbClr val="44546A"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="3810">
+          <a:solidFill>
+            <a:srgbClr val="D6DCE4"/>
+          </a:solidFill>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="44546A"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Sales</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="4472C4"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>Q1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Q2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>Q3</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>Q4</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>80</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>95</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>88</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>110</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="150"/>
+        <c:axId val="1"/>
+        <c:axId val="2"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="2"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1"/>
+              <a:t>preset=minimal</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>A</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="4472C4"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>W1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>W2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>W3</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>W4</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>10</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>20</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>15</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>25</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>B</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="ED7D31"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>W1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>W2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>W3</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>W4</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>8</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>14</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>12</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>20</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+        </c:ser>
+        <c:axId val="1"/>
+        <c:axId val="2"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="808080"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="3810">
+              <a:solidFill>
+                <a:srgbClr val="E0E0E0"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="808080"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="900">
+              <a:solidFill>
+                <a:srgbClr val="808080"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:roundedCorners val="1"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1600" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1600" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>preset=dark</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Sales</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="5B9BD5"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>Q1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Q2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>Q3</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>Q4</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>45</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>60</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>55</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>80</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="150"/>
+        <c:axId val="1"/>
+        <c:axId val="2"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+            <a:solidFill>
+              <a:srgbClr val="555555"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="AAAAAA"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="3810">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+            <a:solidFill>
+              <a:srgbClr val="555555"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="AAAAAA"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:srgbClr val="2D2D2D"/>
+        </a:solidFill>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="900">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:srgbClr val="1E1E1E"/>
+    </a:solidFill>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+      <a:solidFill>
+        <a:srgbClr val="444444"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -570,7 +1305,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd2d5590320284c60"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R16bb2156888d4e3e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -595,12 +1330,12 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
       </xdr:xfrm>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="Rf6a24c20c10f4541"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rea493661dee04a3f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -625,12 +1360,12 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
       </xdr:xfrm>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R0cee95a3c74541c6"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Re557b41a8eda4c51"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -655,12 +1390,12 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
       </xdr:xfrm>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart r:id="Rf8cd0254e80044a5"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R60af46fa167241d9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -670,7 +1405,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -695,7 +1430,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R78a179c76dff47b1"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R4908ebaf4b3646bf"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -720,12 +1455,12 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
       </xdr:xfrm>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart r:id="R2198783de9584fbf"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Ra6022177007d4bdf"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -750,12 +1485,12 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
       </xdr:xfrm>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart r:id="R64dd1f8b75b74fad"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rdd434730e2a84ca8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -780,12 +1515,12 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
       </xdr:xfrm>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart r:id="R0bbc25c9f3874a55"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R4ad3be7fead24a2b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -795,7 +1530,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -820,7 +1555,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rbb72e4056c264836"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rcf5cc70d93c84132"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -845,12 +1580,12 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
       </xdr:xfrm>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart r:id="R2abc1c0547b0408e"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R1ce19ec7a17543af"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -875,12 +1610,12 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
       </xdr:xfrm>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart r:id="R2ec6793ecb5644bf"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rede6a523f2a841e7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -905,12 +1640,12 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
       </xdr:xfrm>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart r:id="Ra8e50eefda8c48a0"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R0a3499650b6047b1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -935,12 +1670,12 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
       </xdr:xfrm>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart r:id="R8bd1f57231744988"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Ree19684747f344e9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -965,12 +1700,12 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
       </xdr:xfrm>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart r:id="Re607355e9bcd47d7"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R77b36aecfff24c35"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -980,7 +1715,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1005,7 +1740,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R98c95a49111d4994"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rfa0cd2b208c445b8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1030,12 +1765,137 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
       </xdr:xfrm>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart r:id="Rb853a41f066d4aab"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rae3545e4d1bd4b6a"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="anchor + preset=corporate"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R38ae65264bec4d0e"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9018d21e3b9b4c63"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="preset=minimal"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rae4ee40434be4ea2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="preset=dark"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rab5a065b748c4abb"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1049,6 +1909,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
+        <cx:f>1-Waterfall &amp; Funnel!$A$2:$A$6</cx:f>
         <cx:lvl ptCount="5">
           <cx:pt idx="0">Leads</cx:pt>
           <cx:pt idx="1">Qualified</cx:pt>
@@ -1058,6 +1919,7 @@
         </cx:lvl>
       </cx:strDim>
       <cx:numDim type="val">
+        <cx:f>1-Waterfall &amp; Funnel!$B$2:$B$6</cx:f>
         <cx:lvl ptCount="5" formatCode="General">
           <cx:pt idx="0">1200</cx:pt>
           <cx:pt idx="1">850</cx:pt>
@@ -1072,8 +1934,8 @@
     <cx:title>
       <cx:tx>
         <cx:rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:r>
               <a:rPr lang="en-US">
                 <a:effectLst>
@@ -1092,19 +1954,23 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="funnel">
+        <cx:series layoutId="funnel" uniqueId="{D07791CF-9675-44C3-BA6D-61E699815084}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>1-Waterfall &amp; Funnel!$B$1</cx:f>
               <cx:v>Pipeline</cx:v>
             </cx:txData>
           </cx:tx>
-          <cx:dataLabels pos="outEnd">
+          <cx:dataLabels>
             <cx:visibility seriesName="0" categoryName="0" value="1"/>
           </cx:dataLabels>
           <cx:dataId val="0"/>
         </cx:series>
       </cx:plotAreaRegion>
+      <cx:axis id="1">
+        <cx:catScaling gapWidth="0.0599999987"/>
+        <cx:tickLabels/>
+      </cx:axis>
     </cx:plotArea>
   </cx:chart>
 </cx:chartSpace>
@@ -1115,6 +1981,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
+        <cx:f>3-Histogram &amp; BoxWhisker!$B$2:$B$18</cx:f>
         <cx:lvl ptCount="17" formatCode="General">
           <cx:pt idx="0">40</cx:pt>
           <cx:pt idx="1">55</cx:pt>
@@ -1141,8 +2008,8 @@
     <cx:title>
       <cx:tx>
         <cx:rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:r>
               <a:rPr lang="en-US"/>
               <a:t>Response Time (outlier bins)</a:t>
@@ -1153,14 +2020,14 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn">
+        <cx:series layoutId="clusteredColumn" uniqueId="{F6720569-3805-41E7-958D-4DEB524C9CCD}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>3-Histogram &amp; BoxWhisker!$B$1</cx:f>
               <cx:v>ms</cx:v>
             </cx:txData>
           </cx:tx>
-          <cx:dataLabels pos="outEnd">
+          <cx:dataLabels>
             <cx:visibility seriesName="0" categoryName="0" value="1"/>
           </cx:dataLabels>
           <cx:dataId val="0"/>
@@ -1188,6 +2055,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
+        <cx:f>3-Histogram &amp; BoxWhisker!$B$2:$B$15</cx:f>
         <cx:lvl ptCount="14">
           <cx:pt idx="0">TeamA</cx:pt>
           <cx:pt idx="1">TeamA</cx:pt>
@@ -1206,6 +2074,7 @@
         </cx:lvl>
       </cx:strDim>
       <cx:numDim type="val">
+        <cx:f>3-Histogram &amp; BoxWhisker!$B$2:$B$15</cx:f>
         <cx:lvl ptCount="14" formatCode="General">
           <cx:pt idx="0">42</cx:pt>
           <cx:pt idx="1">55</cx:pt>
@@ -1226,6 +2095,7 @@
     </cx:data>
     <cx:data id="1">
       <cx:strDim type="cat">
+        <cx:f>3-Histogram &amp; BoxWhisker!$C$2:$C$15</cx:f>
         <cx:lvl ptCount="14">
           <cx:pt idx="0">TeamB</cx:pt>
           <cx:pt idx="1">TeamB</cx:pt>
@@ -1244,6 +2114,7 @@
         </cx:lvl>
       </cx:strDim>
       <cx:numDim type="val">
+        <cx:f>3-Histogram &amp; BoxWhisker!$C$2:$C$15</cx:f>
         <cx:lvl ptCount="14" formatCode="General">
           <cx:pt idx="0">30</cx:pt>
           <cx:pt idx="1">38</cx:pt>
@@ -1267,8 +2138,8 @@
     <cx:title>
       <cx:tx>
         <cx:rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:r>
               <a:rPr lang="en-US"/>
               <a:t>Response Time by Team (ms)</a:t>
@@ -1279,10 +2150,10 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="boxWhisker">
+        <cx:series layoutId="boxWhisker" uniqueId="{107B3AB6-AE94-4CEE-A245-7DE59D272FC7}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>3-Histogram &amp; BoxWhisker!$B$1</cx:f>
               <cx:v>TeamA</cx:v>
             </cx:txData>
           </cx:tx>
@@ -1292,10 +2163,10 @@
             <cx:statistics quartileMethod="exclusive"/>
           </cx:layoutPr>
         </cx:series>
-        <cx:series layoutId="boxWhisker">
+        <cx:series layoutId="boxWhisker" uniqueId="{BFCD8264-729C-4BAC-A38C-8B76DF57C87A}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>3-Histogram &amp; BoxWhisker!$C$1</cx:f>
               <cx:v>TeamB</cx:v>
             </cx:txData>
           </cx:tx>
@@ -1326,6 +2197,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
+        <cx:f>3-Histogram &amp; BoxWhisker!$B$2:$B$14</cx:f>
         <cx:lvl ptCount="13">
           <cx:pt idx="0">Engineering</cx:pt>
           <cx:pt idx="1">Engineering</cx:pt>
@@ -1343,6 +2215,7 @@
         </cx:lvl>
       </cx:strDim>
       <cx:numDim type="val">
+        <cx:f>3-Histogram &amp; BoxWhisker!$B$2:$B$14</cx:f>
         <cx:lvl ptCount="13" formatCode="General">
           <cx:pt idx="0">85</cx:pt>
           <cx:pt idx="1">92</cx:pt>
@@ -1362,6 +2235,7 @@
     </cx:data>
     <cx:data id="1">
       <cx:strDim type="cat">
+        <cx:f>3-Histogram &amp; BoxWhisker!$C$2:$C$13</cx:f>
         <cx:lvl ptCount="12">
           <cx:pt idx="0">Marketing</cx:pt>
           <cx:pt idx="1">Marketing</cx:pt>
@@ -1378,6 +2252,7 @@
         </cx:lvl>
       </cx:strDim>
       <cx:numDim type="val">
+        <cx:f>3-Histogram &amp; BoxWhisker!$C$2:$C$13</cx:f>
         <cx:lvl ptCount="12" formatCode="General">
           <cx:pt idx="0">60</cx:pt>
           <cx:pt idx="1">65</cx:pt>
@@ -1396,6 +2271,7 @@
     </cx:data>
     <cx:data id="2">
       <cx:strDim type="cat">
+        <cx:f>3-Histogram &amp; BoxWhisker!$D$2:$D$14</cx:f>
         <cx:lvl ptCount="13">
           <cx:pt idx="0">Sales</cx:pt>
           <cx:pt idx="1">Sales</cx:pt>
@@ -1413,6 +2289,7 @@
         </cx:lvl>
       </cx:strDim>
       <cx:numDim type="val">
+        <cx:f>3-Histogram &amp; BoxWhisker!$D$2:$D$14</cx:f>
         <cx:lvl ptCount="13" formatCode="General">
           <cx:pt idx="0">55</cx:pt>
           <cx:pt idx="1">62</cx:pt>
@@ -1435,8 +2312,8 @@
     <cx:title>
       <cx:tx>
         <cx:rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:r>
               <a:rPr lang="en-US"/>
               <a:t>Salary Distribution ($k)</a:t>
@@ -1447,10 +2324,10 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="boxWhisker">
+        <cx:series layoutId="boxWhisker" uniqueId="{C59E155E-85CE-4657-A740-851E4D2B1C5C}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>3-Histogram &amp; BoxWhisker!$B$1</cx:f>
               <cx:v>Engineering</cx:v>
             </cx:txData>
           </cx:tx>
@@ -1460,10 +2337,10 @@
             <cx:statistics quartileMethod="inclusive"/>
           </cx:layoutPr>
         </cx:series>
-        <cx:series layoutId="boxWhisker">
+        <cx:series layoutId="boxWhisker" uniqueId="{BAA4CC7F-620C-4A76-BE2F-50FAA74A58CF}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>3-Histogram &amp; BoxWhisker!$C$1</cx:f>
               <cx:v>Marketing</cx:v>
             </cx:txData>
           </cx:tx>
@@ -1473,10 +2350,10 @@
             <cx:statistics quartileMethod="inclusive"/>
           </cx:layoutPr>
         </cx:series>
-        <cx:series layoutId="boxWhisker">
+        <cx:series layoutId="boxWhisker" uniqueId="{8C16DDC6-0537-4B29-A581-BF3EAB519CA2}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>3-Histogram &amp; BoxWhisker!$D$1</cx:f>
               <cx:v>Sales</cx:v>
             </cx:txData>
           </cx:tx>
@@ -1507,6 +2384,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
+        <cx:f>4-Pareto!$A$2:$A$7</cx:f>
         <cx:lvl ptCount="6">
           <cx:pt idx="0">Scratches</cx:pt>
           <cx:pt idx="1">Dents</cx:pt>
@@ -1517,6 +2395,7 @@
         </cx:lvl>
       </cx:strDim>
       <cx:numDim type="val">
+        <cx:f>4-Pareto!$B$2:$B$7</cx:f>
         <cx:lvl ptCount="6" formatCode="General">
           <cx:pt idx="0">45</cx:pt>
           <cx:pt idx="1">30</cx:pt>
@@ -1532,8 +2411,8 @@
     <cx:title>
       <cx:tx>
         <cx:rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:r>
               <a:rPr lang="en-US"/>
               <a:t>Defect Pareto</a:t>
@@ -1544,14 +2423,14 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn">
+        <cx:series layoutId="clusteredColumn" uniqueId="{4E05D8C4-ADE0-4042-8E3D-C74F31311E67}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>4-Pareto!$B$1</cx:f>
               <cx:v>Count</cx:v>
             </cx:txData>
           </cx:tx>
-          <cx:dataLabels pos="outEnd">
+          <cx:dataLabels>
             <cx:visibility seriesName="0" categoryName="0" value="1"/>
           </cx:dataLabels>
           <cx:dataId val="0"/>
@@ -1585,6 +2464,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
+        <cx:f>4-Pareto!$A$2:$A$11</cx:f>
         <cx:lvl ptCount="10">
           <cx:pt idx="0">Config</cx:pt>
           <cx:pt idx="1">Auth</cx:pt>
@@ -1599,6 +2479,7 @@
         </cx:lvl>
       </cx:strDim>
       <cx:numDim type="val">
+        <cx:f>4-Pareto!$B$2:$B$11</cx:f>
         <cx:lvl ptCount="10" formatCode="General">
           <cx:pt idx="0">120</cx:pt>
           <cx:pt idx="1">87</cx:pt>
@@ -1618,8 +2499,8 @@
     <cx:title>
       <cx:tx>
         <cx:rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:r>
               <a:rPr lang="en-US"/>
               <a:t>Root Cause Pareto</a:t>
@@ -1630,10 +2511,10 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn">
+        <cx:series layoutId="clusteredColumn" uniqueId="{F006F790-1971-4A49-AFE2-890E9402FDA9}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>4-Pareto!$B$1</cx:f>
               <cx:v>Tickets</cx:v>
             </cx:txData>
           </cx:tx>
@@ -1669,6 +2550,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
+        <cx:f>1-Waterfall &amp; Funnel!$A$2:$A$7</cx:f>
         <cx:lvl ptCount="6">
           <cx:pt idx="0">Impressions</cx:pt>
           <cx:pt idx="1">Clicks</cx:pt>
@@ -1679,6 +2561,7 @@
         </cx:lvl>
       </cx:strDim>
       <cx:numDim type="val">
+        <cx:f>1-Waterfall &amp; Funnel!$B$2:$B$7</cx:f>
         <cx:lvl ptCount="6" formatCode="General">
           <cx:pt idx="0">10000</cx:pt>
           <cx:pt idx="1">6500</cx:pt>
@@ -1694,8 +2577,8 @@
     <cx:title>
       <cx:tx>
         <cx:rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:r>
               <a:rPr lang="en-US"/>
               <a:t>Marketing Funnel</a:t>
@@ -1706,19 +2589,23 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="funnel">
+        <cx:series layoutId="funnel" uniqueId="{1AA830F7-81E5-40B7-A165-FB7212C112D7}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>1-Waterfall &amp; Funnel!$B$1</cx:f>
               <cx:v>Users</cx:v>
             </cx:txData>
           </cx:tx>
-          <cx:dataLabels pos="outEnd">
+          <cx:dataLabels>
             <cx:visibility seriesName="0" categoryName="0" value="1"/>
           </cx:dataLabels>
           <cx:dataId val="0"/>
         </cx:series>
       </cx:plotAreaRegion>
+      <cx:axis id="1">
+        <cx:catScaling gapWidth="0.0599999987"/>
+        <cx:tickLabels/>
+      </cx:axis>
     </cx:plotArea>
   </cx:chart>
 </cx:chartSpace>
@@ -1729,6 +2616,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
+        <cx:f>2-Treemap &amp; Sunburst!$A$2:$A$9</cx:f>
         <cx:lvl ptCount="8">
           <cx:pt idx="0">Laptops</cx:pt>
           <cx:pt idx="1">Phones</cx:pt>
@@ -1741,6 +2629,7 @@
         </cx:lvl>
       </cx:strDim>
       <cx:numDim type="size">
+        <cx:f>2-Treemap &amp; Sunburst!$B$2:$B$9</cx:f>
         <cx:lvl ptCount="8" formatCode="General">
           <cx:pt idx="0">450</cx:pt>
           <cx:pt idx="1">380</cx:pt>
@@ -1758,8 +2647,8 @@
     <cx:title>
       <cx:tx>
         <cx:rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:r>
               <a:rPr lang="en-US"/>
               <a:t>Revenue by Product</a:t>
@@ -1770,14 +2659,14 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="treemap">
+        <cx:series layoutId="treemap" uniqueId="{37E71C1B-209D-48AA-9D38-475E6E0ABBB1}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>2-Treemap &amp; Sunburst!$B$1</cx:f>
               <cx:v>Revenue</cx:v>
             </cx:txData>
           </cx:tx>
-          <cx:dataLabels pos="outEnd">
+          <cx:dataLabels>
             <cx:visibility seriesName="0" categoryName="0" value="1"/>
           </cx:dataLabels>
           <cx:dataId val="0"/>
@@ -1796,6 +2685,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
+        <cx:f>2-Treemap &amp; Sunburst!$A$2:$A$8</cx:f>
         <cx:lvl ptCount="7">
           <cx:pt idx="0">Engineering</cx:pt>
           <cx:pt idx="1">Sales</cx:pt>
@@ -1807,6 +2697,7 @@
         </cx:lvl>
       </cx:strDim>
       <cx:numDim type="size">
+        <cx:f>2-Treemap &amp; Sunburst!$B$2:$B$8</cx:f>
         <cx:lvl ptCount="7" formatCode="General">
           <cx:pt idx="0">900</cx:pt>
           <cx:pt idx="1">750</cx:pt>
@@ -1823,8 +2714,8 @@
     <cx:title>
       <cx:tx>
         <cx:rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:r>
               <a:rPr lang="en-US" sz="1400" b="1">
                 <a:solidFill>
@@ -1839,10 +2730,10 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="treemap">
+        <cx:series layoutId="treemap" uniqueId="{7971E7B7-30D2-4A6C-A3E1-8E0AF3EA4BC0}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>2-Treemap &amp; Sunburst!$B$1</cx:f>
               <cx:v>Budget</cx:v>
             </cx:txData>
           </cx:tx>
@@ -1862,6 +2753,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
+        <cx:f>2-Treemap &amp; Sunburst!$A$2:$A$11</cx:f>
         <cx:lvl ptCount="10">
           <cx:pt idx="0">A</cx:pt>
           <cx:pt idx="1">B</cx:pt>
@@ -1876,6 +2768,7 @@
         </cx:lvl>
       </cx:strDim>
       <cx:numDim type="size">
+        <cx:f>2-Treemap &amp; Sunburst!$B$2:$B$11</cx:f>
         <cx:lvl ptCount="10" formatCode="General">
           <cx:pt idx="0">250</cx:pt>
           <cx:pt idx="1">200</cx:pt>
@@ -1895,8 +2788,8 @@
     <cx:title>
       <cx:tx>
         <cx:rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:r>
               <a:rPr lang="en-US"/>
               <a:t>Flat Treemap (no parent labels)</a:t>
@@ -1907,14 +2800,14 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="treemap">
+        <cx:series layoutId="treemap" uniqueId="{E5A2032F-84C8-4D82-A28F-4357ABEA38FA}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>2-Treemap &amp; Sunburst!$B$1</cx:f>
               <cx:v>Units</cx:v>
             </cx:txData>
           </cx:tx>
-          <cx:dataLabels pos="outEnd">
+          <cx:dataLabels>
             <cx:visibility seriesName="0" categoryName="0" value="1"/>
           </cx:dataLabels>
           <cx:dataId val="0"/>
@@ -1933,6 +2826,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
+        <cx:f>2-Treemap &amp; Sunburst!$A$2:$A$10</cx:f>
         <cx:lvl ptCount="9">
           <cx:pt idx="0">North</cx:pt>
           <cx:pt idx="1">South</cx:pt>
@@ -1946,6 +2840,7 @@
         </cx:lvl>
       </cx:strDim>
       <cx:numDim type="size">
+        <cx:f>2-Treemap &amp; Sunburst!$B$2:$B$10</cx:f>
         <cx:lvl ptCount="9" formatCode="General">
           <cx:pt idx="0">35</cx:pt>
           <cx:pt idx="1">25</cx:pt>
@@ -1964,8 +2859,8 @@
     <cx:title>
       <cx:tx>
         <cx:rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:r>
               <a:rPr lang="en-US"/>
               <a:t>Market Share by Region</a:t>
@@ -1976,28 +2871,28 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="sunburst">
+        <cx:series layoutId="sunburst" uniqueId="{74C0273F-B5A3-4723-B292-209BD7B96C98}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>2-Treemap &amp; Sunburst!$B$1</cx:f>
               <cx:v>Share</cx:v>
             </cx:txData>
           </cx:tx>
-          <cx:dataLabels pos="outEnd">
+          <cx:dataLabels>
             <cx:visibility seriesName="0" categoryName="0" value="1"/>
           </cx:dataLabels>
           <cx:dataId val="0"/>
         </cx:series>
       </cx:plotAreaRegion>
       <cx:spPr>
-        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:solidFill>
           <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
       </cx:spPr>
     </cx:plotArea>
   </cx:chart>
   <cx:spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="F8FAFC"/>
     </a:solidFill>
   </cx:spPr>
@@ -2009,6 +2904,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
+        <cx:f>3-Histogram &amp; BoxWhisker!$B$2:$B$37</cx:f>
         <cx:lvl ptCount="36" formatCode="General">
           <cx:pt idx="0">45</cx:pt>
           <cx:pt idx="1">52</cx:pt>
@@ -2054,8 +2950,8 @@
     <cx:title>
       <cx:tx>
         <cx:rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:r>
               <a:rPr lang="en-US"/>
               <a:t>Test Scores (auto bins)</a:t>
@@ -2066,10 +2962,10 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn">
+        <cx:series layoutId="clusteredColumn" uniqueId="{F19BFD0F-4032-402A-B806-12474F77B534}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>3-Histogram &amp; BoxWhisker!$B$1</cx:f>
               <cx:v>Scores</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2098,6 +2994,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
+        <cx:f>3-Histogram &amp; BoxWhisker!$B$2:$B$26</cx:f>
         <cx:lvl ptCount="25" formatCode="General">
           <cx:pt idx="0">120</cx:pt>
           <cx:pt idx="1">135</cx:pt>
@@ -2132,8 +3029,8 @@
     <cx:title>
       <cx:tx>
         <cx:rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:r>
               <a:rPr lang="en-US"/>
               <a:t>Sales (binCount=5)</a:t>
@@ -2144,10 +3041,10 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn">
+        <cx:series layoutId="clusteredColumn" uniqueId="{46D8CAF8-B41F-4A69-AE39-0DB40E017326}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>3-Histogram &amp; BoxWhisker!$B$1</cx:f>
               <cx:v>Sales</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2178,6 +3075,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
+        <cx:f>3-Histogram &amp; BoxWhisker!$B$2:$B$26</cx:f>
         <cx:lvl ptCount="25" formatCode="General">
           <cx:pt idx="0">120</cx:pt>
           <cx:pt idx="1">135</cx:pt>
@@ -2212,8 +3110,8 @@
     <cx:title>
       <cx:tx>
         <cx:rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:r>
               <a:rPr lang="en-US"/>
               <a:t>Sales (binSize=50)</a:t>
@@ -2224,14 +3122,14 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn">
+        <cx:series layoutId="clusteredColumn" uniqueId="{FF9094B6-A272-40A7-B108-639FDF938326}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>3-Histogram &amp; BoxWhisker!$B$1</cx:f>
               <cx:v>Sales</cx:v>
             </cx:txData>
           </cx:tx>
-          <cx:dataLabels pos="outEnd">
+          <cx:dataLabels>
             <cx:visibility seriesName="0" categoryName="0" value="1"/>
           </cx:dataLabels>
           <cx:dataId val="0"/>
@@ -9393,29 +10291,535 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R187062ad137b4c1f"/>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="B1" t="str">
+        <x:v>Users</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>Impressions</x:v>
+      </x:c>
+      <x:c r="B2" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>Clicks</x:v>
+      </x:c>
+      <x:c r="B3" t="n">
+        <x:v>6500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>Signups</x:v>
+      </x:c>
+      <x:c r="B4" t="n">
+        <x:v>3200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="B5" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Paying</x:v>
+      </x:c>
+      <x:c r="B6" t="n">
+        <x:v>900</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Retained</x:v>
+      </x:c>
+      <x:c r="B7" t="n">
+        <x:v>450</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a1b59d1d47b42f5"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R540f10767d46406f"/>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="B1" t="str">
+        <x:v>Share</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>North</x:v>
+      </x:c>
+      <x:c r="B2" t="n">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>South</x:v>
+      </x:c>
+      <x:c r="B3" t="n">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>East</x:v>
+      </x:c>
+      <x:c r="B4" t="n">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>West</x:v>
+      </x:c>
+      <x:c r="B5" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Urban</x:v>
+      </x:c>
+      <x:c r="B6" t="n">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Suburban</x:v>
+      </x:c>
+      <x:c r="B7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>Rural</x:v>
+      </x:c>
+      <x:c r="B8" t="n">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Online</x:v>
+      </x:c>
+      <x:c r="B9" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Retail</x:v>
+      </x:c>
+      <x:c r="B10" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>J</x:v>
+      </x:c>
+      <x:c r="B11" t="n">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R871e20c96f1347f4"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9df9983a3241481c"/>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="B1" t="str">
+        <x:v>Engineering</x:v>
+      </x:c>
+      <x:c r="C1" t="str">
+        <x:v>Marketing</x:v>
+      </x:c>
+      <x:c r="D1" t="str">
+        <x:v>Sales</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="B2" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C2" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D2" t="n">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="B3" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C3" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D3" t="n">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="B4" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C4" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D4" t="n">
+        <x:v>68</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="B5" t="n">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C5" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D5" t="n">
+        <x:v>75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="B6" t="n">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C6" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="B7" t="n">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C7" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D7" t="n">
+        <x:v>90</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="B8" t="n">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="C8" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D8" t="n">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="B9" t="n">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="C9" t="n">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D9" t="n">
+        <x:v>105</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="B10" t="n">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="C10" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D10" t="n">
+        <x:v>115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="B11" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="C11" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D11" t="n">
+        <x:v>125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="B12" t="n">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="C12" t="n">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D12" t="n">
+        <x:v>140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="B13" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="C13" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D13" t="n">
+        <x:v>160</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="B14" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="C14" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D14" t="n">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="B15" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="C15" t="n">
+        <x:v>110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="B16" t="n">
+        <x:v>220</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="B17" t="n">
+        <x:v>280</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="B18" t="n">
+        <x:v>350</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="B19" t="n">
+        <x:v>310</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="B20" t="n">
+        <x:v>340</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="B21" t="n">
+        <x:v>380</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="B22" t="n">
+        <x:v>420</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="B23" t="n">
+        <x:v>480</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="B24" t="n">
+        <x:v>550</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="B25" t="n">
+        <x:v>620</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="B26" t="n">
+        <x:v>700</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="B27" t="n">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="B28" t="n">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="B29" t="n">
+        <x:v>89</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="B30" t="n">
+        <x:v>90</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="B31" t="n">
+        <x:v>91</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="B32" t="n">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="B33" t="n">
+        <x:v>93</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="B34" t="n">
+        <x:v>94</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="B35" t="n">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="B36" t="n">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="B37" t="n">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec4fa5fd03fe4f0d"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="B1" t="str">
+        <x:v>Tickets</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>Network</x:v>
+      </x:c>
+      <x:c r="B2" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>Auth</x:v>
+      </x:c>
+      <x:c r="B3" t="n">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>DB</x:v>
+      </x:c>
+      <x:c r="B4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>Cache</x:v>
+      </x:c>
+      <x:c r="B5" t="n">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>UI</x:v>
+      </x:c>
+      <x:c r="B6" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Config</x:v>
+      </x:c>
+      <x:c r="B7" t="n">
+        <x:v>120</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>Deploy</x:v>
+      </x:c>
+      <x:c r="B8" t="n">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Monitor</x:v>
+      </x:c>
+      <x:c r="B9" t="n">
+        <x:v>67</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Queue</x:v>
+      </x:c>
+      <x:c r="B10" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Storage</x:v>
+      </x:c>
+      <x:c r="B11" t="n">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbaf173fdad76458a"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b2e9fa3971144ae"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0015d122a6be4c4d"/>
 </x:worksheet>
 </file>